--- a/INA-SPA-CONSOLIDATED-FINAL.xlsx
+++ b/INA-SPA-CONSOLIDATED-FINAL.xlsx
@@ -6863,7 +6863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7589,6 +7589,9 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
@@ -7604,7 +7607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8330,6 +8333,9 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
@@ -8345,7 +8351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9071,6 +9077,9 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
